--- a/docs/Memgine_Collect_W37-W65_Test_Tracker.xlsx
+++ b/docs/Memgine_Collect_W37-W65_Test_Tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MynikaTech\memgine\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C0F7048-83A3-4D87-B2CE-4D5221E33DB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36EA7C4F-2159-4F92-AEDF-EDD4F77ABF34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="179">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="181">
   <si>
     <t>MEMGINE  |  Poynt Collect — Remote Customer E2E Tests</t>
   </si>
@@ -557,6 +557,12 @@
   </si>
   <si>
     <t>Missing - Google Pay unsupported browser test</t>
+  </si>
+  <si>
+    <t>Tested using Chrome DevTools network throttling (5,000 ms latency). Payment button displayed PROCESSING, Check Payment Status appeared briefly, and payment completed successfully. No premature failure observed.  Limitation: Simulated browser latency, not a controlled delay within Poynt's backend.</t>
+  </si>
+  <si>
+    <t>Notes</t>
   </si>
 </sst>
 </file>
@@ -716,8 +722,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="CollectE2ETests" displayName="CollectE2ETests" ref="A5:I34" totalsRowShown="0">
-  <tableColumns count="9">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="CollectE2ETests" displayName="CollectE2ETests" ref="A5:J34" totalsRowShown="0">
+  <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Test ID"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Scenario"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Expected result"/>
@@ -727,6 +733,7 @@
     <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Existing unit coverage (baseline)"/>
     <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Completion / remaining validation"/>
     <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Integration / browser status"/>
+    <tableColumn id="10" xr3:uid="{AD3B5C00-83B3-4369-BA3E-2248181E8D6A}" name="Notes"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -927,7 +934,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I34"/>
+  <dimension ref="A1:J34"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -939,9 +946,10 @@
     <col min="7" max="7" width="54" customWidth="1"/>
     <col min="8" max="8" width="65" customWidth="1"/>
     <col min="9" max="9" width="23" customWidth="1"/>
+    <col min="10" max="10" width="45.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="33.950000000000003" customHeight="1">
+    <row r="1" spans="1:10" ht="33.950000000000003" customHeight="1">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -954,7 +962,7 @@
       <c r="H1" s="7"/>
       <c r="I1" s="7"/>
     </row>
-    <row r="2" spans="1:9" ht="24" customHeight="1">
+    <row r="2" spans="1:10" ht="24" customHeight="1">
       <c r="A2" s="8" t="s">
         <v>1</v>
       </c>
@@ -967,7 +975,7 @@
       <c r="H2" s="8"/>
       <c r="I2" s="8"/>
     </row>
-    <row r="3" spans="1:9" ht="26.1" customHeight="1">
+    <row r="3" spans="1:10" ht="26.1" customHeight="1">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -979,14 +987,14 @@
       </c>
       <c r="D3" s="1">
         <f>COUNTIF(I6:I34,"Passed")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F3" s="1">
         <f>COUNTIF(I6:I34,"Not started")+COUNTIF(I6:I34,"In progress")+COUNTIF(I6:I34,"Blocked")</f>
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>5</v>
@@ -997,7 +1005,7 @@
       </c>
       <c r="I3" s="1"/>
     </row>
-    <row r="5" spans="1:9" ht="32.1" customHeight="1">
+    <row r="5" spans="1:10" ht="32.1" customHeight="1">
       <c r="A5" s="2" t="s">
         <v>6</v>
       </c>
@@ -1025,8 +1033,11 @@
       <c r="I5" s="2" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="6" spans="1:9" ht="54" customHeight="1">
+      <c r="J5" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="54" customHeight="1">
       <c r="A6" s="4" t="s">
         <v>15</v>
       </c>
@@ -1055,7 +1066,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="54" customHeight="1">
+    <row r="7" spans="1:10" ht="54" customHeight="1">
       <c r="A7" s="4" t="s">
         <v>24</v>
       </c>
@@ -1081,10 +1092,13 @@
         <v>31</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" ht="54" customHeight="1">
+        <v>19</v>
+      </c>
+      <c r="J7" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="54" customHeight="1">
       <c r="A8" s="4" t="s">
         <v>32</v>
       </c>
@@ -1113,7 +1127,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="54" customHeight="1">
+    <row r="9" spans="1:10" ht="54" customHeight="1">
       <c r="A9" s="4" t="s">
         <v>37</v>
       </c>
@@ -1142,7 +1156,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="54" customHeight="1">
+    <row r="10" spans="1:10" ht="54" customHeight="1">
       <c r="A10" s="4" t="s">
         <v>44</v>
       </c>
@@ -1171,7 +1185,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="54" customHeight="1">
+    <row r="11" spans="1:10" ht="54" customHeight="1">
       <c r="A11" s="4" t="s">
         <v>50</v>
       </c>
@@ -1200,7 +1214,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="54" customHeight="1">
+    <row r="12" spans="1:10" ht="54" customHeight="1">
       <c r="A12" s="4" t="s">
         <v>55</v>
       </c>
@@ -1229,7 +1243,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="54" customHeight="1">
+    <row r="13" spans="1:10" ht="54" customHeight="1">
       <c r="A13" s="4" t="s">
         <v>60</v>
       </c>
@@ -1258,7 +1272,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="54" customHeight="1">
+    <row r="14" spans="1:10" ht="54" customHeight="1">
       <c r="A14" s="4" t="s">
         <v>67</v>
       </c>
@@ -1287,7 +1301,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="54" customHeight="1">
+    <row r="15" spans="1:10" ht="54" customHeight="1">
       <c r="A15" s="4" t="s">
         <v>74</v>
       </c>
@@ -1316,7 +1330,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="54" customHeight="1">
+    <row r="16" spans="1:10" ht="54" customHeight="1">
       <c r="A16" s="4" t="s">
         <v>78</v>
       </c>
